--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD60301-42E4-4ADA-AEF4-3D96566447DD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5AE32D-7086-4B67-890C-22D1638E2DD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="104">
   <si>
     <t>#</t>
   </si>
@@ -139,9 +139,6 @@
     <t>RES SMD 10K OHM 1% 1/20W 0201</t>
   </si>
   <si>
-    <t>20.5kΩ 50mW Thick Film Resistor ±1% ±200ppm/℃ 0201 Chip Resistor - Surface Mount RoHS</t>
-  </si>
-  <si>
     <t>-55℃~+125℃ 0Ω 25V 50mW Thick Film Resistor ±1% 0201 Chip Resistor - Surface Mount ROHS</t>
   </si>
   <si>
@@ -229,9 +226,6 @@
     <t>RC0201FR-0710KL</t>
   </si>
   <si>
-    <t>AC0201FR-0720K5L</t>
-  </si>
-  <si>
     <t>RC0201FR-070RL</t>
   </si>
   <si>
@@ -329,6 +323,15 @@
   </si>
   <si>
     <t>Battery Holders, Clips, Contacts RoHS</t>
+  </si>
+  <si>
+    <t>20.5kΩ ±1% 50mW 0201 Thick Film Resistor</t>
+  </si>
+  <si>
+    <t>RTT012052FTH</t>
+  </si>
+  <si>
+    <t>RALEC</t>
   </si>
 </sst>
 </file>
@@ -864,22 +867,22 @@
         <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -893,19 +896,19 @@
         <v>7</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" s="7">
         <v>1</v>
@@ -928,16 +931,16 @@
         <v>27</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J4" s="9">
         <v>2</v>
@@ -958,16 +961,16 @@
         <v>28</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J5" s="7">
         <v>2</v>
@@ -990,16 +993,16 @@
         <v>29</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J6" s="9">
         <v>1</v>
@@ -1020,16 +1023,16 @@
         <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -1050,16 +1053,16 @@
         <v>31</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J8" s="9">
         <v>4</v>
@@ -1082,16 +1085,16 @@
         <v>32</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -1112,16 +1115,16 @@
         <v>33</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J10" s="9">
         <v>2</v>
@@ -1144,16 +1147,16 @@
         <v>34</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J11" s="7">
         <v>3</v>
@@ -1176,16 +1179,16 @@
         <v>35</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J12" s="9">
         <v>6</v>
@@ -1208,16 +1211,16 @@
         <v>36</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J13" s="7">
         <v>2</v>
@@ -1240,16 +1243,16 @@
         <v>37</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J14" s="9">
         <v>4</v>
@@ -1272,23 +1275,23 @@
         <v>38</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -1301,19 +1304,19 @@
         <v>20</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J16" s="9">
         <v>1</v>
@@ -1333,19 +1336,19 @@
         <v>21</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J17" s="7">
         <v>1</v>
@@ -1365,19 +1368,19 @@
         <v>22</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -1398,12 +1401,12 @@
         <v>26</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="7"/>
       <c r="I19" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -1423,19 +1426,19 @@
         <v>24</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J20" s="9">
         <v>1</v>
@@ -1453,19 +1456,19 @@
         <v>25</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J21" s="7">
         <v>1</v>

--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5AE32D-7086-4B67-890C-22D1638E2DD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB26048A-DA36-4FAE-9B55-5776CF8A8D5B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -332,6 +332,18 @@
   </si>
   <si>
     <t>RALEC</t>
+  </si>
+  <si>
+    <t>LCM0720A3134F</t>
+  </si>
+  <si>
+    <t>LEADER</t>
+  </si>
+  <si>
+    <t>Flat Vibration Motor 3V Motors - AC, DC RoHS</t>
+  </si>
+  <si>
+    <t>Motor</t>
   </si>
 </sst>
 </file>
@@ -402,7 +414,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -493,11 +505,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -536,6 +559,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -824,7 +850,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="3.109375" style="4" customWidth="1"/>
@@ -1475,6 +1501,23 @@
       </c>
       <c r="K21" s="7"/>
     </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D22" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="15">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:K1"/>

--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB26048A-DA36-4FAE-9B55-5776CF8A8D5B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519D4B53-C6D7-46F3-A831-7B1A6601C57D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -343,7 +343,25 @@
     <t>Flat Vibration Motor 3V Motors - AC, DC RoHS</t>
   </si>
   <si>
-    <t>Motor</t>
+    <t>TP1</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+  <si>
+    <t>CR1225 Coin Cell</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>cr1225</t>
+  </si>
+  <si>
+    <t>Renata</t>
+  </si>
+  <si>
+    <t>https://www.chipsmall.com/Products/CR1225_31316158.html</t>
   </si>
 </sst>
 </file>
@@ -359,14 +377,27 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color indexed="13"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -374,21 +405,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -522,45 +539,49 @@
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -850,672 +871,697 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="10"/>
+    <col min="2" max="2" width="3.109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="10" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.44140625" style="10" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+    </row>
+    <row r="2" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="11">
+    <row r="3" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="13">
         <f>ROW(B3) - ROW($B$2)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="14"/>
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="1">
         <v>1</v>
       </c>
-      <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11">
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="13">
         <f t="shared" ref="B4:B20" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="3">
         <v>2</v>
       </c>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="11">
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="13">
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="1">
         <v>2</v>
       </c>
-      <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="11">
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="13">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="3">
         <v>1</v>
       </c>
-      <c r="K6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="11">
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="13">
         <f>ROW(B7) - ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="14"/>
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="1">
         <v>1</v>
       </c>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1"/>
-      <c r="B8" s="11">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="13">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="9" t="s">
+      <c r="C8" s="15"/>
+      <c r="D8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="3">
         <v>4</v>
       </c>
-      <c r="K8" s="9"/>
-    </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1"/>
-      <c r="B9" s="11">
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="13">
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="1">
         <v>1</v>
       </c>
-      <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1"/>
-      <c r="B10" s="11">
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="13">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="9" t="s">
+      <c r="C10" s="15"/>
+      <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="3">
         <v>2</v>
       </c>
-      <c r="K10" s="9"/>
-    </row>
-    <row r="11" spans="1:11" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1"/>
-      <c r="B11" s="11">
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="13">
         <f>ROW(B11) - ROW($B$2)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="1">
         <v>3</v>
       </c>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="11">
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="13">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="3">
         <v>6</v>
       </c>
-      <c r="K12" s="9"/>
-    </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="1"/>
-      <c r="B13" s="11">
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="13">
         <f>ROW(B13) - ROW($B$2)</f>
         <v>11</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="1">
         <v>2</v>
       </c>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="1"/>
-      <c r="B14" s="11">
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="13">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="3">
         <v>4</v>
       </c>
-      <c r="K14" s="9"/>
-    </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="1"/>
-      <c r="B15" s="11">
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="13">
         <f>ROW(B15) - ROW($B$2)</f>
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="1">
         <v>1</v>
       </c>
-      <c r="K15" s="7"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1"/>
-      <c r="B16" s="11">
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="13">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="3">
         <v>1</v>
       </c>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1"/>
-      <c r="B17" s="11">
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="13">
         <f>ROW(B17) - ROW($B$2)</f>
         <v>15</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="1">
         <v>1</v>
       </c>
-      <c r="K17" s="7"/>
-    </row>
-    <row r="18" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1"/>
-      <c r="B18" s="11">
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="13">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="3">
         <v>1</v>
       </c>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1"/>
-      <c r="B19" s="11">
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="13">
         <f>ROW(B19) - ROW($B$2)</f>
         <v>17</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="8" t="s">
+      <c r="G19" s="2"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="1">
         <v>1</v>
       </c>
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1"/>
-      <c r="B20" s="11">
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="13">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="9">
+      <c r="J20" s="3">
         <v>1</v>
       </c>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="B21" s="11">
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="13">
         <f>ROW(B21) - ROW($B$2)</f>
         <v>19</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="7" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="1">
         <v>1</v>
       </c>
-      <c r="K21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D22" s="15" t="s">
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D22" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="5">
         <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D23" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
+++ b/Design Files/SamirAbiNahed-DigitalTasbeeh/Deliverables/BOM/Client-BOM_SamirAbiNahed-DigitalTasbeeh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\embedded Designers\LocAl\SamirAbiNahed-DigitalTasbeeh\PCB\SamirAbiNahed-DigitalTasbeeh\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519D4B53-C6D7-46F3-A831-7B1A6601C57D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{338C18AB-BEBB-41BB-B76B-D35CE15BE2A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="117">
   <si>
     <t>#</t>
   </si>
@@ -91,9 +91,6 @@
     <t>R16</t>
   </si>
   <si>
-    <t>SW1</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -178,9 +175,6 @@
     <t>Res-0201</t>
   </si>
   <si>
-    <t>EVQPLH_PAN</t>
-  </si>
-  <si>
     <t>VQFN-20-EP(3x3)</t>
   </si>
   <si>
@@ -313,9 +307,6 @@
     <t>13.3k</t>
   </si>
   <si>
-    <t>EVQ-PLHA15</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -362,6 +353,24 @@
   </si>
   <si>
     <t>https://www.chipsmall.com/Products/CR1225_31316158.html</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>Tactile Switch SPST 160gf 1.5mm SMD (SMT) Tab 5.2mm x 5.2mm Surface Mount</t>
+  </si>
+  <si>
+    <t>GT-TC084A-H015-L5</t>
+  </si>
+  <si>
+    <t>G-Switch</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>Motor</t>
   </si>
 </sst>
 </file>
@@ -431,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -449,69 +458,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -522,45 +472,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -569,20 +487,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,694 +795,720 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="10"/>
-    <col min="2" max="2" width="3.109375" style="10" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30" style="10" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.44140625" style="10" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="1" width="8.88671875" style="3"/>
+    <col min="2" max="2" width="3.109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="3" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.44140625" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7"/>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-    </row>
-    <row r="2" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="11" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="13">
+      <c r="E2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="6">
         <f>ROW(B3) - ROW($B$2)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="E3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" s="8">
         <v>1</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="13">
+      <c r="K3" s="8"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="6">
         <f t="shared" ref="B4:B20" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="J4" s="3">
+      <c r="E4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="8">
         <v>2</v>
       </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="13">
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="6">
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="E5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="8">
         <v>2</v>
       </c>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="13">
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="E6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="8">
         <v>1</v>
       </c>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="13">
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="6">
         <f>ROW(B7) - ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="E7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="8">
         <v>1</v>
       </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="13">
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="3" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="E8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="8">
         <v>4</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="13">
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="6">
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="E9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="8">
         <v>1</v>
       </c>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="13">
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="7"/>
+      <c r="D10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="E10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="8">
         <v>2</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" ht="48.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="13">
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="48" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="6">
         <f>ROW(B11) - ROW($B$2)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="E11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="8">
         <v>3</v>
       </c>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="13">
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="6">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="E12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J12" s="8">
         <v>6</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="13">
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="6">
         <f>ROW(B13) - ROW($B$2)</f>
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="E13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J13" s="8">
         <v>2</v>
       </c>
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="13">
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="6">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="E14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J14" s="8">
         <v>4</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="13">
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="6">
         <f>ROW(B15) - ROW($B$2)</f>
         <v>13</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="E15" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="8">
         <v>1</v>
       </c>
-      <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="13">
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="B16" s="6">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J16" s="3">
+      <c r="E16" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J16" s="8">
         <v>1</v>
       </c>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="13">
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="6">
         <f>ROW(B17) - ROW($B$2)</f>
         <v>15</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="E17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="8">
         <v>1</v>
       </c>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="13">
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="6">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="E18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J18" s="8">
         <v>1</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="13">
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" spans="1:11" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="6">
         <f>ROW(B19) - ROW($B$2)</f>
         <v>17</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="C19" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J19" s="8">
         <v>1</v>
       </c>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="13">
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="8">
         <v>1</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="13">
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21" spans="1:11" ht="36" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="6">
         <f>ROW(B21) - ROW($B$2)</f>
         <v>19</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="C21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="8">
         <v>1</v>
       </c>
-      <c r="K21" s="1"/>
+      <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D22" s="5" t="s">
+      <c r="B22" s="6">
+        <f t="shared" ref="B22:B23" si="1">ROW(B22) - ROW($B$2)</f>
+        <v>20</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="8">
+        <v>1</v>
+      </c>
+      <c r="K22" s="9"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="J22" s="5">
+      <c r="G23" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D23" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F23" s="6" t="s">
+      <c r="K23" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J23" s="5">
-        <v>1</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
